--- a/wishlist_valentin.xlsx
+++ b/wishlist_valentin.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a5351de14e4a67c9/Downloads/wishlist/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cfn7021\Downloads\wishlist\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="37" documentId="13_ncr:1_{64E338DB-40B6-4262-9583-6B45DA59074D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B1C475E0-DDFC-45F3-9B47-1B1BD8F412EB}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{541DF9F1-FB17-40D0-9E15-6838C8BE3D25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3645" yWindow="1890" windowWidth="21600" windowHeight="11295" xr2:uid="{FE4DC328-739C-48AF-B2EF-9BDF321350CE}"/>
+    <workbookView xWindow="5070" yWindow="615" windowWidth="29010" windowHeight="23385" xr2:uid="{FE4DC328-739C-48AF-B2EF-9BDF321350CE}"/>
   </bookViews>
   <sheets>
     <sheet name="Wishlist Valentin" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Wishlist Valentin'!$A$1:$E$53</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Wishlist Valentin'!$A$1:$E$58</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="224">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="223">
   <si>
     <t>Image</t>
   </si>
@@ -204,9 +204,6 @@
     <t>Microsoft Xbox Wireless Controller + Wireless Adapter for Windows 10</t>
   </si>
   <si>
-    <t>Y</t>
-  </si>
-  <si>
     <t>https://www.digitec.ch/im/productimages/7/1/8/8/4/0/4/7/9/5/1/1/9/9/5/6/4/3/6/346792b0-7f82-443e-ae90-080215b6cb79_cropped.jpg?impolicy=ProductTileImage&amp;resizeWidth=500&amp;resizeHeight=375&amp;cropWidth=500&amp;cropHeight=375&amp;resizeType=downsize&amp;quality=high</t>
   </si>
   <si>
@@ -636,9 +633,6 @@
     <t>SKIP</t>
   </si>
   <si>
-    <t>SKIP (skip) / Y (reserved) / GAP (formatting gap)</t>
-  </si>
-  <si>
     <t>GAP</t>
   </si>
   <si>
@@ -712,6 +706,9 @@
   </si>
   <si>
     <t>https://m.media-amazon.com/images/I/71IHLi5qPLL._SL1500_.jpg</t>
+  </si>
+  <si>
+    <t>SKIP (skip: hide from display) / Y (reserved: show faded out) / GAP (formatting gap)</t>
   </si>
 </sst>
 </file>
@@ -801,10 +798,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1112,7 +1105,7 @@
     <col min="2" max="2" width="26.140625" customWidth="1"/>
     <col min="3" max="3" width="53.140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="46.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="79" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1129,7 +1122,7 @@
         <v>2</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>198</v>
+        <v>222</v>
       </c>
     </row>
     <row r="2" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
@@ -1137,7 +1130,7 @@
         <v>4</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>30</v>
@@ -1146,7 +1139,7 @@
         <v>5</v>
       </c>
       <c r="E2" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="3" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
@@ -1163,7 +1156,7 @@
         <v>9</v>
       </c>
       <c r="E3" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="4" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
@@ -1180,7 +1173,7 @@
         <v>51</v>
       </c>
       <c r="E4" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="5" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
@@ -1197,7 +1190,7 @@
         <v>16</v>
       </c>
       <c r="E5" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="6" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
@@ -1214,7 +1207,7 @@
         <v>28</v>
       </c>
       <c r="E6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="7" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
@@ -1231,7 +1224,7 @@
         <v>21</v>
       </c>
       <c r="E7" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="8" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
@@ -1248,7 +1241,7 @@
         <v>27</v>
       </c>
       <c r="E8" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="9" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
@@ -1265,7 +1258,7 @@
         <v>36</v>
       </c>
       <c r="E9" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="10" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
@@ -1282,74 +1275,83 @@
         <v>37</v>
       </c>
       <c r="E10" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
+        <v>193</v>
+      </c>
+      <c r="B11" t="s">
+        <v>192</v>
+      </c>
+      <c r="C11" t="s">
         <v>194</v>
       </c>
-      <c r="B11" t="s">
-        <v>193</v>
-      </c>
-      <c r="C11" t="s">
+      <c r="D11" t="s">
         <v>195</v>
       </c>
-      <c r="D11" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E11" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
+        <v>199</v>
+      </c>
+      <c r="B12" t="s">
         <v>201</v>
       </c>
-      <c r="B12" t="s">
-        <v>203</v>
-      </c>
       <c r="C12" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="D12" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+        <v>198</v>
+      </c>
+      <c r="E12" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="B13" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="C13" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="D13" t="s">
         <v>9</v>
       </c>
+      <c r="E13" t="s">
+        <v>196</v>
+      </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>212</v>
-      </c>
-      <c r="B14" t="s">
-        <v>222</v>
+        <v>40</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>143</v>
       </c>
       <c r="C14" t="s">
-        <v>219</v>
-      </c>
-      <c r="D14" s="3">
-        <v>40</v>
+        <v>39</v>
+      </c>
+      <c r="D14" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B15" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="C15" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="D15" s="3">
         <v>40</v>
@@ -1357,214 +1359,214 @@
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
+        <v>209</v>
+      </c>
+      <c r="B16" t="s">
+        <v>221</v>
+      </c>
+      <c r="C16" t="s">
+        <v>218</v>
+      </c>
+      <c r="D16" s="3">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>181</v>
+      </c>
+      <c r="B17" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="B16" s="1" t="s">
-        <v>183</v>
-      </c>
-      <c r="C16" t="s">
+      <c r="C17" t="s">
+        <v>179</v>
+      </c>
+      <c r="D17" t="s">
         <v>180</v>
       </c>
-      <c r="D16" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>210</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="C17" t="s">
-        <v>218</v>
-      </c>
-      <c r="D17" s="3">
-        <v>40</v>
+      <c r="E17" t="s">
+        <v>196</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
+        <v>208</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="C18" t="s">
+        <v>216</v>
+      </c>
+      <c r="D18" s="3">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>205</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="C19" t="s">
+        <v>206</v>
+      </c>
+      <c r="D19" s="3" t="s">
         <v>207</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="C18" t="s">
-        <v>208</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>44</v>
-      </c>
-      <c r="B19" t="s">
-        <v>43</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="D19" t="s">
-        <v>45</v>
-      </c>
-      <c r="E19" t="s">
-        <v>197</v>
       </c>
     </row>
     <row r="20" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B20" t="s">
-        <v>47</v>
-      </c>
-      <c r="C20" t="s">
-        <v>46</v>
+        <v>43</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="D20" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="E20" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="21" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="B21" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="C21" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="D21" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="E21" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="22" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="B22" t="s">
-        <v>61</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>60</v>
+        <v>56</v>
+      </c>
+      <c r="C22" t="s">
+        <v>55</v>
       </c>
       <c r="D22" t="s">
-        <v>28</v>
+        <v>57</v>
       </c>
       <c r="E22" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="23" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B23" t="s">
-        <v>65</v>
-      </c>
-      <c r="C23" t="s">
-        <v>64</v>
+        <v>60</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>59</v>
       </c>
       <c r="D23" t="s">
-        <v>89</v>
+        <v>28</v>
       </c>
       <c r="E23" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="24" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="B24" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="C24" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="D24" t="s">
-        <v>69</v>
+        <v>88</v>
       </c>
       <c r="E24" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="25" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="B25" t="s">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="C25" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="D25" t="s">
-        <v>79</v>
+        <v>68</v>
       </c>
       <c r="E25" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="26" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B26" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C26" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D26" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="E26" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="27" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B27" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C27" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D27" t="s">
         <v>79</v>
       </c>
       <c r="E27" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="28" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>88</v>
+        <v>71</v>
       </c>
       <c r="B28" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="C28" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="D28" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="E28" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="29" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
@@ -1572,490 +1574,495 @@
         <v>87</v>
       </c>
       <c r="B29" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="C29" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="D29" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="E29" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="30" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>99</v>
+        <v>86</v>
       </c>
       <c r="B30" t="s">
-        <v>97</v>
+        <v>85</v>
       </c>
       <c r="C30" t="s">
-        <v>96</v>
+        <v>83</v>
       </c>
       <c r="D30" t="s">
-        <v>98</v>
+        <v>84</v>
       </c>
       <c r="E30" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="31" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
+        <v>98</v>
+      </c>
+      <c r="B31" t="s">
+        <v>96</v>
+      </c>
+      <c r="C31" t="s">
+        <v>95</v>
+      </c>
+      <c r="D31" t="s">
+        <v>97</v>
+      </c>
+      <c r="E31" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>99</v>
+      </c>
+      <c r="B32" t="s">
         <v>100</v>
       </c>
-      <c r="B31" t="s">
+      <c r="C32" t="s">
         <v>101</v>
       </c>
-      <c r="C31" t="s">
+      <c r="D32" t="s">
         <v>102</v>
       </c>
-      <c r="D31" t="s">
+      <c r="E32" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
         <v>103</v>
       </c>
-      <c r="E31" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
+      <c r="B33" t="s">
+        <v>106</v>
+      </c>
+      <c r="C33" t="s">
         <v>104</v>
       </c>
-      <c r="B32" t="s">
+      <c r="D33" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
         <v>107</v>
       </c>
-      <c r="C32" t="s">
-        <v>105</v>
-      </c>
-      <c r="D32" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
+      <c r="B34" t="s">
         <v>108</v>
       </c>
-      <c r="B33" t="s">
+      <c r="C34" t="s">
         <v>109</v>
       </c>
-      <c r="C33" t="s">
+      <c r="D34" t="s">
         <v>110</v>
       </c>
-      <c r="D33" t="s">
-        <v>111</v>
-      </c>
-      <c r="E33" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>112</v>
-      </c>
-      <c r="B34" t="s">
-        <v>113</v>
-      </c>
-      <c r="C34" t="s">
-        <v>114</v>
-      </c>
-      <c r="D34" t="s">
-        <v>115</v>
+      <c r="E34" t="s">
+        <v>196</v>
       </c>
     </row>
     <row r="35" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="B35" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="C35" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="D35" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="E35" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="36" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="B36" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="C36" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="D36" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="E36" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="37" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="B37" t="s">
-        <v>129</v>
+        <v>121</v>
       </c>
       <c r="C37" t="s">
-        <v>130</v>
+        <v>119</v>
       </c>
       <c r="D37" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="E37" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="38" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
+        <v>127</v>
+      </c>
+      <c r="B38" t="s">
+        <v>128</v>
+      </c>
+      <c r="C38" t="s">
+        <v>129</v>
+      </c>
+      <c r="D38" t="s">
+        <v>130</v>
+      </c>
+      <c r="E38" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>123</v>
+      </c>
+      <c r="B39" t="s">
+        <v>125</v>
+      </c>
+      <c r="C39" t="s">
         <v>124</v>
       </c>
-      <c r="B38" t="s">
+      <c r="D39" t="s">
         <v>126</v>
       </c>
-      <c r="C38" t="s">
-        <v>125</v>
-      </c>
-      <c r="D38" t="s">
-        <v>127</v>
-      </c>
-      <c r="E38" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
-        <v>40</v>
-      </c>
-      <c r="B39" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="C39" t="s">
-        <v>39</v>
-      </c>
-      <c r="D39" t="s">
-        <v>41</v>
+      <c r="E39" t="s">
+        <v>196</v>
       </c>
     </row>
     <row r="40" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
+        <v>137</v>
+      </c>
+      <c r="B40" t="s">
         <v>138</v>
       </c>
-      <c r="B40" t="s">
-        <v>139</v>
-      </c>
       <c r="C40" t="s">
+        <v>135</v>
+      </c>
+      <c r="D40" t="s">
         <v>136</v>
       </c>
-      <c r="D40" t="s">
-        <v>137</v>
-      </c>
       <c r="E40" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
+        <v>144</v>
+      </c>
+      <c r="B41" t="s">
         <v>145</v>
       </c>
-      <c r="B41" t="s">
+      <c r="C41" t="s">
         <v>146</v>
       </c>
-      <c r="C41" t="s">
+      <c r="D41" t="s">
         <v>147</v>
       </c>
-      <c r="D41" t="s">
-        <v>148</v>
+      <c r="E41" t="s">
+        <v>196</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>151</v>
-      </c>
-      <c r="B42" t="s">
+        <v>13</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D42" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
         <v>150</v>
       </c>
-      <c r="C42" t="s">
+      <c r="B43" t="s">
         <v>149</v>
       </c>
-      <c r="D42" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
-        <v>155</v>
-      </c>
-      <c r="B43" t="s">
-        <v>152</v>
-      </c>
       <c r="C43" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="D43" t="s">
-        <v>154</v>
-      </c>
-      <c r="E43" t="s">
-        <v>197</v>
+        <v>114</v>
       </c>
     </row>
     <row r="44" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="B44" t="s">
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="C44" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="D44" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="E44" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="45" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>175</v>
+        <v>155</v>
       </c>
       <c r="B45" t="s">
+        <v>158</v>
+      </c>
+      <c r="C45" t="s">
+        <v>156</v>
+      </c>
+      <c r="D45" t="s">
+        <v>157</v>
+      </c>
+      <c r="E45" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>174</v>
+      </c>
+      <c r="B46" t="s">
+        <v>171</v>
+      </c>
+      <c r="C46" t="s">
         <v>172</v>
       </c>
-      <c r="C45" t="s">
+      <c r="D46" t="s">
         <v>173</v>
       </c>
-      <c r="D45" t="s">
-        <v>174</v>
-      </c>
-      <c r="E45" t="s">
+      <c r="E46" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E47" t="s">
         <v>197</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="E46" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A47" t="s">
-        <v>13</v>
-      </c>
-      <c r="B47" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C47" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D47" t="s">
-        <v>12</v>
-      </c>
-      <c r="E47" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
+        <v>131</v>
+      </c>
+      <c r="B48" t="s">
         <v>132</v>
       </c>
-      <c r="B48" t="s">
+      <c r="C48" t="s">
         <v>133</v>
       </c>
-      <c r="C48" t="s">
+      <c r="D48" t="s">
         <v>134</v>
       </c>
-      <c r="D48" t="s">
-        <v>135</v>
-      </c>
       <c r="E48" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="E49" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
+        <v>139</v>
+      </c>
+      <c r="B50" t="s">
+        <v>141</v>
+      </c>
+      <c r="C50" t="s">
         <v>140</v>
       </c>
-      <c r="B50" t="s">
+      <c r="D50" t="s">
         <v>142</v>
       </c>
-      <c r="C50" t="s">
-        <v>141</v>
-      </c>
-      <c r="D50" t="s">
-        <v>143</v>
-      </c>
       <c r="E50" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
+        <v>167</v>
+      </c>
+      <c r="B51" t="s">
         <v>168</v>
       </c>
-      <c r="B51" t="s">
+      <c r="C51" t="s">
         <v>169</v>
       </c>
-      <c r="C51" t="s">
+      <c r="D51" t="s">
         <v>170</v>
       </c>
-      <c r="D51" t="s">
-        <v>171</v>
-      </c>
       <c r="E51" s="4" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
+        <v>92</v>
+      </c>
+      <c r="B52" t="s">
+        <v>191</v>
+      </c>
+      <c r="C52" t="s">
         <v>93</v>
       </c>
-      <c r="B52" t="s">
-        <v>192</v>
-      </c>
-      <c r="C52" t="s">
+      <c r="D52" t="s">
         <v>94</v>
       </c>
-      <c r="D52" t="s">
-        <v>95</v>
-      </c>
       <c r="E52" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
+        <v>183</v>
+      </c>
+      <c r="B53" t="s">
+        <v>186</v>
+      </c>
+      <c r="C53" t="s">
         <v>184</v>
       </c>
-      <c r="B53" t="s">
+      <c r="D53" t="s">
+        <v>185</v>
+      </c>
+      <c r="E53" s="4" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>89</v>
+      </c>
+      <c r="B54" t="s">
+        <v>190</v>
+      </c>
+      <c r="C54" t="s">
+        <v>90</v>
+      </c>
+      <c r="D54" t="s">
+        <v>91</v>
+      </c>
+      <c r="E54" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>189</v>
+      </c>
+      <c r="B55" t="s">
         <v>187</v>
       </c>
-      <c r="C53" t="s">
-        <v>185</v>
-      </c>
-      <c r="D53" t="s">
-        <v>186</v>
-      </c>
-      <c r="E53" s="4" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A54" t="s">
-        <v>90</v>
-      </c>
-      <c r="B54" t="s">
-        <v>191</v>
-      </c>
-      <c r="C54" t="s">
-        <v>91</v>
-      </c>
-      <c r="D54" t="s">
-        <v>92</v>
-      </c>
-      <c r="E54" s="4" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A55" t="s">
-        <v>190</v>
-      </c>
-      <c r="B55" t="s">
+      <c r="C55" t="s">
         <v>188</v>
-      </c>
-      <c r="C55" t="s">
-        <v>189</v>
       </c>
       <c r="D55" s="3">
         <v>40</v>
       </c>
       <c r="E55" s="4" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
+        <v>161</v>
+      </c>
+      <c r="B56" t="s">
+        <v>160</v>
+      </c>
+      <c r="C56" t="s">
+        <v>159</v>
+      </c>
+      <c r="D56" t="s">
         <v>162</v>
       </c>
-      <c r="B56" t="s">
-        <v>161</v>
-      </c>
-      <c r="C56" t="s">
-        <v>160</v>
-      </c>
-      <c r="D56" t="s">
+      <c r="E56" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>166</v>
+      </c>
+      <c r="B57" t="s">
+        <v>165</v>
+      </c>
+      <c r="C57" t="s">
         <v>163</v>
       </c>
-      <c r="E56" s="4" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A57" t="s">
-        <v>167</v>
-      </c>
-      <c r="B57" t="s">
-        <v>166</v>
-      </c>
-      <c r="C57" t="s">
+      <c r="D57" t="s">
         <v>164</v>
       </c>
-      <c r="D57" t="s">
-        <v>165</v>
-      </c>
-      <c r="E57" s="4" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E57" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
+        <v>175</v>
+      </c>
+      <c r="B58" t="s">
+        <v>177</v>
+      </c>
+      <c r="C58" t="s">
         <v>176</v>
       </c>
-      <c r="B58" t="s">
+      <c r="D58" t="s">
         <v>178</v>
       </c>
-      <c r="C58" t="s">
-        <v>177</v>
-      </c>
-      <c r="D58" t="s">
-        <v>179</v>
-      </c>
-      <c r="E58" s="4" t="s">
-        <v>54</v>
+      <c r="E58" t="s">
+        <v>196</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E53" xr:uid="{2CF9E297-72DE-4386-8002-570237626454}">
+  <autoFilter ref="A1:E58" xr:uid="{2CF9E297-72DE-4386-8002-570237626454}">
     <filterColumn colId="4">
       <filters blank="1">
         <filter val="GAP"/>
-        <filter val="Y"/>
       </filters>
     </filterColumn>
   </autoFilter>
@@ -2064,16 +2071,22 @@
   </sortState>
   <hyperlinks>
     <hyperlink ref="B3" r:id="rId1" xr:uid="{88D7FD61-7495-433B-BB0E-0F6A89ABE74A}"/>
-    <hyperlink ref="B47" r:id="rId2" xr:uid="{63CC93D1-B3B9-4AD9-8A03-C49E71BB178F}"/>
+    <hyperlink ref="B42" r:id="rId2" xr:uid="{63CC93D1-B3B9-4AD9-8A03-C49E71BB178F}"/>
     <hyperlink ref="B5" r:id="rId3" xr:uid="{BE3001C8-C6F4-4958-8E83-375C8631FFD0}"/>
     <hyperlink ref="C6" r:id="rId4" xr:uid="{B0629CDA-CE4C-4A68-98F2-514ED65E6764}"/>
     <hyperlink ref="B6" r:id="rId5" xr:uid="{E8D94EF1-4592-45B9-B8B2-6EE34CDA156B}"/>
-    <hyperlink ref="C19" r:id="rId6" xr:uid="{5F8F8A1D-DECA-423A-B681-8EB6D1C72089}"/>
-    <hyperlink ref="C22" r:id="rId7" xr:uid="{EA0AE655-D84E-4CA0-B64D-234DB4B1F86A}"/>
-    <hyperlink ref="B16" r:id="rId8" xr:uid="{962EF1F7-F1F1-425B-85D9-C19696DDDA8A}"/>
+    <hyperlink ref="C20" r:id="rId6" xr:uid="{5F8F8A1D-DECA-423A-B681-8EB6D1C72089}"/>
+    <hyperlink ref="C23" r:id="rId7" xr:uid="{EA0AE655-D84E-4CA0-B64D-234DB4B1F86A}"/>
+    <hyperlink ref="B17" r:id="rId8" xr:uid="{962EF1F7-F1F1-425B-85D9-C19696DDDA8A}"/>
     <hyperlink ref="C49" r:id="rId9" xr:uid="{9CC374CE-9746-4369-A4C1-2ED078F270F4}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId10"/>
 </worksheet>
+</file>
+
+<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{ff6dbec8-95a8-4638-9f5f-bd076536645c}" enabled="1" method="Standard" siteId="{5dbf1add-202a-4b8d-815b-bf0fb024e033}" contentBits="0" removed="0"/>
+</clbl:labelList>
 </file>
--- a/wishlist_valentin.xlsx
+++ b/wishlist_valentin.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cfn7021\Downloads\wishlist\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{541DF9F1-FB17-40D0-9E15-6838C8BE3D25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90EE9ED8-1B20-431F-B009-F68070893082}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5070" yWindow="615" windowWidth="29010" windowHeight="23385" xr2:uid="{FE4DC328-739C-48AF-B2EF-9BDF321350CE}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="29010" windowHeight="23385" xr2:uid="{FE4DC328-739C-48AF-B2EF-9BDF321350CE}"/>
   </bookViews>
   <sheets>
     <sheet name="Wishlist Valentin" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="223">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="226">
   <si>
     <t>Image</t>
   </si>
@@ -492,9 +492,6 @@
     <t>https://www.lego.com/cdn/cs/set/assets/bltc38b5911d77d1733/10350_Prod.png?format=webply&amp;fit=bounds&amp;quality=75&amp;width=1200&amp;height=1200&amp;dpr=1</t>
   </si>
   <si>
-    <t>LEGO 10350 Tudor Corner</t>
-  </si>
-  <si>
     <t>https://c0.iggcdn.com/indiegogo-media-prod-cld/image/upload/c_fill,g_center,q_auto,f_auto,h_506,w_762/fuxofrj2akskjdvfimjn</t>
   </si>
   <si>
@@ -709,6 +706,18 @@
   </si>
   <si>
     <t>SKIP (skip: hide from display) / Y (reserved: show faded out) / GAP (formatting gap)</t>
+  </si>
+  <si>
+    <t>https://www.lego.com/en-ch/product/shopping-street-11371</t>
+  </si>
+  <si>
+    <t>https://www.lego.com/cdn/cs/set/assets/blt8d68c03655d85c6a/11371_boxprod_v39_en-gb.png?format=webply&amp;fit=bounds&amp;quality=75&amp;width=1200&amp;height=1200&amp;dpr=1</t>
+  </si>
+  <si>
+    <t>LEGO® 10350 Tudor Corner</t>
+  </si>
+  <si>
+    <t>LEGO® 11371 Shopping Street</t>
   </si>
 </sst>
 </file>
@@ -776,12 +785,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="6" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1098,7 +1110,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2CF9E297-72DE-4386-8002-570237626454}">
   <sheetPr filterMode="1"/>
-  <dimension ref="A1:E58"/>
+  <dimension ref="A1:E59"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="37.85546875" customWidth="1"/>
@@ -1122,7 +1134,7 @@
         <v>2</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="2" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
@@ -1139,7 +1151,7 @@
         <v>5</v>
       </c>
       <c r="E2" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="3" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
@@ -1156,7 +1168,7 @@
         <v>9</v>
       </c>
       <c r="E3" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="4" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
@@ -1173,7 +1185,7 @@
         <v>51</v>
       </c>
       <c r="E4" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="5" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
@@ -1190,7 +1202,7 @@
         <v>16</v>
       </c>
       <c r="E5" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="6" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
@@ -1207,7 +1219,7 @@
         <v>28</v>
       </c>
       <c r="E6" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="7" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
@@ -1224,7 +1236,7 @@
         <v>21</v>
       </c>
       <c r="E7" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="8" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
@@ -1241,7 +1253,7 @@
         <v>27</v>
       </c>
       <c r="E8" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="9" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
@@ -1258,7 +1270,7 @@
         <v>36</v>
       </c>
       <c r="E9" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="10" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
@@ -1275,58 +1287,58 @@
         <v>37</v>
       </c>
       <c r="E10" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="11" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
+        <v>192</v>
+      </c>
+      <c r="B11" t="s">
+        <v>191</v>
+      </c>
+      <c r="C11" t="s">
         <v>193</v>
       </c>
-      <c r="B11" t="s">
-        <v>192</v>
-      </c>
-      <c r="C11" t="s">
+      <c r="D11" t="s">
         <v>194</v>
       </c>
-      <c r="D11" t="s">
-        <v>195</v>
-      </c>
       <c r="E11" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
+        <v>198</v>
+      </c>
+      <c r="B12" t="s">
+        <v>200</v>
+      </c>
+      <c r="C12" t="s">
         <v>199</v>
       </c>
-      <c r="B12" t="s">
-        <v>201</v>
-      </c>
-      <c r="C12" t="s">
-        <v>200</v>
-      </c>
       <c r="D12" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E12" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="13" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B13" t="s">
+        <v>210</v>
+      </c>
+      <c r="C13" t="s">
         <v>211</v>
-      </c>
-      <c r="C13" t="s">
-        <v>212</v>
       </c>
       <c r="D13" t="s">
         <v>9</v>
       </c>
       <c r="E13" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
@@ -1345,13 +1357,13 @@
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B15" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C15" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D15" s="3">
         <v>40</v>
@@ -1359,13 +1371,13 @@
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B16" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C16" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D16" s="3">
         <v>40</v>
@@ -1373,30 +1385,30 @@
     </row>
     <row r="17" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
+        <v>180</v>
+      </c>
+      <c r="B17" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="B17" s="1" t="s">
-        <v>182</v>
-      </c>
       <c r="C17" t="s">
+        <v>178</v>
+      </c>
+      <c r="D17" t="s">
         <v>179</v>
       </c>
-      <c r="D17" t="s">
-        <v>180</v>
-      </c>
       <c r="E17" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C18" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D18" s="3">
         <v>40</v>
@@ -1404,16 +1416,16 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
+        <v>204</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="C19" t="s">
         <v>205</v>
       </c>
-      <c r="B19" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="C19" t="s">
+      <c r="D19" s="3" t="s">
         <v>206</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>207</v>
       </c>
     </row>
     <row r="20" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
@@ -1430,7 +1442,7 @@
         <v>45</v>
       </c>
       <c r="E20" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="21" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
@@ -1447,7 +1459,7 @@
         <v>49</v>
       </c>
       <c r="E21" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="22" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
@@ -1464,7 +1476,7 @@
         <v>57</v>
       </c>
       <c r="E22" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="23" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
@@ -1481,7 +1493,7 @@
         <v>28</v>
       </c>
       <c r="E23" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="24" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
@@ -1498,7 +1510,7 @@
         <v>88</v>
       </c>
       <c r="E24" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="25" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
@@ -1515,7 +1527,7 @@
         <v>68</v>
       </c>
       <c r="E25" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="26" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
@@ -1532,7 +1544,7 @@
         <v>78</v>
       </c>
       <c r="E26" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="27" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
@@ -1549,7 +1561,7 @@
         <v>79</v>
       </c>
       <c r="E27" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="28" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
@@ -1566,7 +1578,7 @@
         <v>78</v>
       </c>
       <c r="E28" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="29" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
@@ -1583,7 +1595,7 @@
         <v>81</v>
       </c>
       <c r="E29" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="30" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
@@ -1600,7 +1612,7 @@
         <v>84</v>
       </c>
       <c r="E30" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="31" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
@@ -1617,7 +1629,7 @@
         <v>97</v>
       </c>
       <c r="E31" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="32" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
@@ -1634,7 +1646,7 @@
         <v>102</v>
       </c>
       <c r="E32" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
@@ -1665,7 +1677,7 @@
         <v>110</v>
       </c>
       <c r="E34" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="35" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
@@ -1682,7 +1694,7 @@
         <v>114</v>
       </c>
       <c r="E35" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="36" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
@@ -1699,7 +1711,7 @@
         <v>117</v>
       </c>
       <c r="E36" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="37" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
@@ -1716,7 +1728,7 @@
         <v>122</v>
       </c>
       <c r="E37" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="38" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
@@ -1733,7 +1745,7 @@
         <v>130</v>
       </c>
       <c r="E38" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="39" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
@@ -1750,7 +1762,7 @@
         <v>126</v>
       </c>
       <c r="E39" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="40" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
@@ -1767,7 +1779,7 @@
         <v>136</v>
       </c>
       <c r="E40" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="41" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
@@ -1784,7 +1796,7 @@
         <v>147</v>
       </c>
       <c r="E41" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
@@ -1803,7 +1815,7 @@
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>150</v>
+        <v>224</v>
       </c>
       <c r="B43" t="s">
         <v>149</v>
@@ -1817,58 +1829,67 @@
     </row>
     <row r="44" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B44" t="s">
+        <v>150</v>
+      </c>
+      <c r="C44" t="s">
         <v>151</v>
       </c>
-      <c r="C44" t="s">
+      <c r="D44" t="s">
         <v>152</v>
       </c>
-      <c r="D44" t="s">
-        <v>153</v>
-      </c>
       <c r="E44" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="45" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
+        <v>154</v>
+      </c>
+      <c r="B45" t="s">
+        <v>157</v>
+      </c>
+      <c r="C45" t="s">
         <v>155</v>
       </c>
-      <c r="B45" t="s">
-        <v>158</v>
-      </c>
-      <c r="C45" t="s">
+      <c r="D45" t="s">
         <v>156</v>
       </c>
-      <c r="D45" t="s">
-        <v>157</v>
-      </c>
       <c r="E45" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="46" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B46" t="s">
+        <v>170</v>
+      </c>
+      <c r="C46" t="s">
         <v>171</v>
       </c>
-      <c r="C46" t="s">
+      <c r="D46" t="s">
         <v>172</v>
       </c>
-      <c r="D46" t="s">
-        <v>173</v>
-      </c>
       <c r="E46" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="E47" t="s">
-        <v>197</v>
+      <c r="A47" s="5" t="s">
+        <v>225</v>
+      </c>
+      <c r="B47" t="s">
+        <v>223</v>
+      </c>
+      <c r="C47" t="s">
+        <v>222</v>
+      </c>
+      <c r="D47" t="s">
+        <v>114</v>
       </c>
     </row>
     <row r="48" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
@@ -1885,24 +1906,24 @@
         <v>134</v>
       </c>
       <c r="E48" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="49" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C49" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="D49" s="3" t="s">
         <v>202</v>
       </c>
-      <c r="D49" s="3" t="s">
-        <v>203</v>
-      </c>
       <c r="E49" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="50" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
@@ -1919,24 +1940,24 @@
         <v>142</v>
       </c>
       <c r="E50" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="51" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
+        <v>166</v>
+      </c>
+      <c r="B51" t="s">
         <v>167</v>
       </c>
-      <c r="B51" t="s">
+      <c r="C51" t="s">
         <v>168</v>
       </c>
-      <c r="C51" t="s">
+      <c r="D51" t="s">
         <v>169</v>
       </c>
-      <c r="D51" t="s">
-        <v>170</v>
-      </c>
       <c r="E51" s="4" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="52" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
@@ -1944,7 +1965,7 @@
         <v>92</v>
       </c>
       <c r="B52" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C52" t="s">
         <v>93</v>
@@ -1953,24 +1974,24 @@
         <v>94</v>
       </c>
       <c r="E52" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="53" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
+        <v>182</v>
+      </c>
+      <c r="B53" t="s">
+        <v>185</v>
+      </c>
+      <c r="C53" t="s">
         <v>183</v>
       </c>
-      <c r="B53" t="s">
-        <v>186</v>
-      </c>
-      <c r="C53" t="s">
+      <c r="D53" t="s">
         <v>184</v>
       </c>
-      <c r="D53" t="s">
-        <v>185</v>
-      </c>
       <c r="E53" s="4" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="54" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
@@ -1978,7 +1999,7 @@
         <v>89</v>
       </c>
       <c r="B54" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C54" t="s">
         <v>90</v>
@@ -1987,74 +2008,79 @@
         <v>91</v>
       </c>
       <c r="E54" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="55" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B55" t="s">
+        <v>186</v>
+      </c>
+      <c r="C55" t="s">
         <v>187</v>
-      </c>
-      <c r="C55" t="s">
-        <v>188</v>
       </c>
       <c r="D55" s="3">
         <v>40</v>
       </c>
       <c r="E55" s="4" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="56" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
+        <v>160</v>
+      </c>
+      <c r="B56" t="s">
+        <v>159</v>
+      </c>
+      <c r="C56" t="s">
+        <v>158</v>
+      </c>
+      <c r="D56" t="s">
         <v>161</v>
       </c>
-      <c r="B56" t="s">
-        <v>160</v>
-      </c>
-      <c r="C56" t="s">
-        <v>159</v>
-      </c>
-      <c r="D56" t="s">
-        <v>162</v>
-      </c>
       <c r="E56" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="57" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B57" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C57" t="s">
+        <v>162</v>
+      </c>
+      <c r="D57" t="s">
         <v>163</v>
       </c>
-      <c r="D57" t="s">
-        <v>164</v>
-      </c>
       <c r="E57" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="58" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
+        <v>174</v>
+      </c>
+      <c r="B58" t="s">
+        <v>176</v>
+      </c>
+      <c r="C58" t="s">
         <v>175</v>
       </c>
-      <c r="B58" t="s">
+      <c r="D58" t="s">
         <v>177</v>
       </c>
-      <c r="C58" t="s">
-        <v>176</v>
-      </c>
-      <c r="D58" t="s">
-        <v>178</v>
-      </c>
       <c r="E58" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E59" t="s">
         <v>196</v>
       </c>
     </row>

--- a/wishlist_valentin.xlsx
+++ b/wishlist_valentin.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cfn7021\Downloads\wishlist\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90EE9ED8-1B20-431F-B009-F68070893082}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{473355C5-59DF-4791-BEC4-5108CE84790F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="29010" windowHeight="23385" xr2:uid="{FE4DC328-739C-48AF-B2EF-9BDF321350CE}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{FE4DC328-739C-48AF-B2EF-9BDF321350CE}"/>
   </bookViews>
   <sheets>
     <sheet name="Wishlist Valentin" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="226">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="234">
   <si>
     <t>Image</t>
   </si>
@@ -718,6 +718,30 @@
   </si>
   <si>
     <t>LEGO® 11371 Shopping Street</t>
+  </si>
+  <si>
+    <t>https://www.lego.com/cdn/cs/set/assets/bltba98a80df3c8c659/blt1b09b2c445792134-11375_WEB_SEC01_NOBG.png?format=webply&amp;fit=bounds&amp;quality=75&amp;width=1200&amp;height=1200&amp;dpr=1</t>
+  </si>
+  <si>
+    <t>https://www.lego.com/en-ch/product/ferrari-f2004-michael-schumacher-11375</t>
+  </si>
+  <si>
+    <t>100 CHF</t>
+  </si>
+  <si>
+    <t>LEGO® 11375 Ferrari F2004 &amp; Michael Schumacher</t>
+  </si>
+  <si>
+    <t>LEGO® 11504 Peace Lily</t>
+  </si>
+  <si>
+    <t>https://www.lego.com/en-ch/product/peace-lily-11504</t>
+  </si>
+  <si>
+    <t>https://www.lego.com/cdn/cs/set/assets/bltf61cb3273fb972f3/11504_Prod_en-gb.png?format=webply&amp;fit=bounds&amp;quality=75&amp;width=1200&amp;height=1200&amp;dpr=1</t>
+  </si>
+  <si>
+    <t>70 CHF</t>
   </si>
 </sst>
 </file>
@@ -1110,7 +1134,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2CF9E297-72DE-4386-8002-570237626454}">
   <sheetPr filterMode="1"/>
-  <dimension ref="A1:E59"/>
+  <dimension ref="A1:E63"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="37.85546875" customWidth="1"/>
@@ -2080,7 +2104,35 @@
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="E59" t="s">
+      <c r="A59" t="s">
+        <v>229</v>
+      </c>
+      <c r="B59" t="s">
+        <v>226</v>
+      </c>
+      <c r="C59" t="s">
+        <v>227</v>
+      </c>
+      <c r="D59" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>230</v>
+      </c>
+      <c r="B60" t="s">
+        <v>232</v>
+      </c>
+      <c r="C60" t="s">
+        <v>231</v>
+      </c>
+      <c r="D60" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E63" t="s">
         <v>196</v>
       </c>
     </row>

--- a/wishlist_valentin.xlsx
+++ b/wishlist_valentin.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cfn7021\Downloads\wishlist\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a5351de14e4a67c9/Downloads/wishlist/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{473355C5-59DF-4791-BEC4-5108CE84790F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="22" documentId="14_{7808EC8F-397C-4CFC-A707-B713EAAA428B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{86A62E19-EBBD-42D7-9FEA-98EE900EFCE7}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{FE4DC328-739C-48AF-B2EF-9BDF321350CE}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{FE4DC328-739C-48AF-B2EF-9BDF321350CE}"/>
   </bookViews>
   <sheets>
     <sheet name="Wishlist Valentin" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="234">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="254">
   <si>
     <t>Image</t>
   </si>
@@ -742,6 +742,66 @@
   </si>
   <si>
     <t>70 CHF</t>
+  </si>
+  <si>
+    <t>https://store.steampowered.com/app/3357650/PRAGMATA/</t>
+  </si>
+  <si>
+    <t>60 CHF</t>
+  </si>
+  <si>
+    <t>https://shared.akamai.steamstatic.com/store_item_assets/steam/apps/3357650/e32e168b25ed68a0cf6264c220c07e96c2abfb56/header.jpg?t=1776235822</t>
+  </si>
+  <si>
+    <t>Joc Steam: Pragmata</t>
+  </si>
+  <si>
+    <t>https://regatuljocurilor.ro/ro/acasa/-the-fellowship-of-the-ring-trick-taking-game-english-edition</t>
+  </si>
+  <si>
+    <t>https://regatuljocurilor.ro/135082-large_default/-the-fellowship-of-the-ring-trick-taking-game-english-edition.jpg</t>
+  </si>
+  <si>
+    <t>The Fellowship of the Ring: Trick-Taking Game (English Edition)</t>
+  </si>
+  <si>
+    <t>23 CHF</t>
+  </si>
+  <si>
+    <t>Arkham Horror: The Card Game - Chapter Two Core Set (EN)</t>
+  </si>
+  <si>
+    <t>https://www.fantasywelt.de/Arkham-Horror-The-Card-Game-Chapter-Two-Core-Set-EN_1</t>
+  </si>
+  <si>
+    <t>62 EUR</t>
+  </si>
+  <si>
+    <t>https://www.fantasywelt.de/media/image/product/217055/lg/arkham-horror-the-card-game-chapter-two-core-set-en.jpg</t>
+  </si>
+  <si>
+    <t>PureRef Business</t>
+  </si>
+  <si>
+    <t>50 USD</t>
+  </si>
+  <si>
+    <t>https://www.pureref.com/download.php</t>
+  </si>
+  <si>
+    <t>https://www.pureref.com/images/PureRef.svg</t>
+  </si>
+  <si>
+    <t>Joc Steam: Esoteric Ebb</t>
+  </si>
+  <si>
+    <t>https://store.steampowered.com/app/2057760/Esoteric_Ebb/</t>
+  </si>
+  <si>
+    <t>25 CHF</t>
+  </si>
+  <si>
+    <t>https://shared.akamai.steamstatic.com/store_item_assets/steam/apps/2057760/3fc3e737678a0d5db6816609bec2c9c6f2c11a88/header.jpg?t=1776091835</t>
   </si>
 </sst>
 </file>
@@ -1134,7 +1194,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2CF9E297-72DE-4386-8002-570237626454}">
   <sheetPr filterMode="1"/>
-  <dimension ref="A1:E63"/>
+  <dimension ref="A1:E66"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="37.85546875" customWidth="1"/>
@@ -2131,9 +2191,79 @@
         <v>233</v>
       </c>
     </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E61" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>237</v>
+      </c>
+      <c r="B62" t="s">
+        <v>236</v>
+      </c>
+      <c r="C62" t="s">
+        <v>234</v>
+      </c>
+      <c r="D62" t="s">
+        <v>235</v>
+      </c>
+    </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="E63" t="s">
-        <v>196</v>
+      <c r="A63" t="s">
+        <v>240</v>
+      </c>
+      <c r="B63" t="s">
+        <v>239</v>
+      </c>
+      <c r="C63" t="s">
+        <v>238</v>
+      </c>
+      <c r="D63" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>242</v>
+      </c>
+      <c r="B64" t="s">
+        <v>245</v>
+      </c>
+      <c r="C64" t="s">
+        <v>243</v>
+      </c>
+      <c r="D64" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>246</v>
+      </c>
+      <c r="B65" t="s">
+        <v>249</v>
+      </c>
+      <c r="C65" t="s">
+        <v>248</v>
+      </c>
+      <c r="D65" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>250</v>
+      </c>
+      <c r="B66" t="s">
+        <v>253</v>
+      </c>
+      <c r="C66" t="s">
+        <v>251</v>
+      </c>
+      <c r="D66" t="s">
+        <v>252</v>
       </c>
     </row>
   </sheetData>

--- a/wishlist_valentin.xlsx
+++ b/wishlist_valentin.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a5351de14e4a67c9/Downloads/wishlist/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="22" documentId="14_{7808EC8F-397C-4CFC-A707-B713EAAA428B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{86A62E19-EBBD-42D7-9FEA-98EE900EFCE7}"/>
+  <xr:revisionPtr revIDLastSave="23" documentId="14_{7808EC8F-397C-4CFC-A707-B713EAAA428B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9686DF3F-74BF-4F2F-B15F-AB9446300D90}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{FE4DC328-739C-48AF-B2EF-9BDF321350CE}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="29010" windowHeight="23385" xr2:uid="{FE4DC328-739C-48AF-B2EF-9BDF321350CE}"/>
   </bookViews>
   <sheets>
     <sheet name="Wishlist Valentin" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Wishlist Valentin'!$A$1:$E$58</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Wishlist Valentin'!$A$1:$E$59</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="254">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="309" uniqueCount="254">
   <si>
     <t>Image</t>
   </si>
@@ -894,6 +894,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1194,7 +1198,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2CF9E297-72DE-4386-8002-570237626454}">
   <sheetPr filterMode="1"/>
-  <dimension ref="A1:E66"/>
+  <dimension ref="A1:E67"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="37.85546875" customWidth="1"/>
@@ -1427,120 +1431,117 @@
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>40</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>143</v>
+        <v>139</v>
+      </c>
+      <c r="B14" t="s">
+        <v>141</v>
       </c>
       <c r="C14" t="s">
-        <v>39</v>
-      </c>
-      <c r="D14" t="s">
-        <v>41</v>
+        <v>140</v>
+      </c>
+      <c r="D14" s="3">
+        <v>160</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>209</v>
-      </c>
-      <c r="B15" t="s">
-        <v>219</v>
+        <v>40</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>143</v>
       </c>
       <c r="C15" t="s">
-        <v>216</v>
-      </c>
-      <c r="D15" s="3">
-        <v>40</v>
+        <v>39</v>
+      </c>
+      <c r="D15" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B16" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C16" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D16" s="3">
         <v>40</v>
       </c>
     </row>
-    <row r="17" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
+        <v>208</v>
+      </c>
+      <c r="B17" t="s">
+        <v>220</v>
+      </c>
+      <c r="C17" t="s">
+        <v>217</v>
+      </c>
+      <c r="D17" s="3">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
         <v>180</v>
       </c>
-      <c r="B17" s="1" t="s">
+      <c r="B18" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="C17" t="s">
+      <c r="C18" t="s">
         <v>178</v>
       </c>
-      <c r="D17" t="s">
+      <c r="D18" t="s">
         <v>179</v>
       </c>
-      <c r="E17" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>207</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>218</v>
-      </c>
-      <c r="C18" t="s">
-        <v>215</v>
-      </c>
-      <c r="D18" s="3">
-        <v>40</v>
+      <c r="E18" t="s">
+        <v>195</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
+        <v>207</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="C19" t="s">
+        <v>215</v>
+      </c>
+      <c r="D19" s="3">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
         <v>204</v>
       </c>
-      <c r="B19" s="1" t="s">
+      <c r="B20" s="1" t="s">
         <v>214</v>
       </c>
-      <c r="C19" t="s">
+      <c r="C20" t="s">
         <v>205</v>
       </c>
-      <c r="D19" s="3" t="s">
+      <c r="D20" s="3" t="s">
         <v>206</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>44</v>
-      </c>
-      <c r="B20" t="s">
-        <v>43</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="D20" t="s">
-        <v>45</v>
-      </c>
-      <c r="E20" t="s">
-        <v>195</v>
       </c>
     </row>
     <row r="21" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B21" t="s">
-        <v>47</v>
-      </c>
-      <c r="C21" t="s">
-        <v>46</v>
+        <v>43</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="D21" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="E21" t="s">
         <v>195</v>
@@ -1548,16 +1549,16 @@
     </row>
     <row r="22" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="B22" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="C22" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="D22" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="E22" t="s">
         <v>195</v>
@@ -1565,16 +1566,16 @@
     </row>
     <row r="23" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="B23" t="s">
-        <v>60</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>59</v>
+        <v>56</v>
+      </c>
+      <c r="C23" t="s">
+        <v>55</v>
       </c>
       <c r="D23" t="s">
-        <v>28</v>
+        <v>57</v>
       </c>
       <c r="E23" t="s">
         <v>195</v>
@@ -1582,16 +1583,16 @@
     </row>
     <row r="24" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B24" t="s">
-        <v>64</v>
-      </c>
-      <c r="C24" t="s">
-        <v>63</v>
+        <v>60</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>59</v>
       </c>
       <c r="D24" t="s">
-        <v>88</v>
+        <v>28</v>
       </c>
       <c r="E24" t="s">
         <v>195</v>
@@ -1599,16 +1600,16 @@
     </row>
     <row r="25" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="B25" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C25" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="D25" t="s">
-        <v>68</v>
+        <v>88</v>
       </c>
       <c r="E25" t="s">
         <v>195</v>
@@ -1616,16 +1617,16 @@
     </row>
     <row r="26" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="B26" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="C26" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="D26" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="E26" t="s">
         <v>195</v>
@@ -1633,16 +1634,16 @@
     </row>
     <row r="27" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B27" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C27" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D27" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E27" t="s">
         <v>195</v>
@@ -1650,16 +1651,16 @@
     </row>
     <row r="28" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B28" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C28" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D28" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E28" t="s">
         <v>195</v>
@@ -1667,16 +1668,16 @@
     </row>
     <row r="29" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>87</v>
+        <v>71</v>
       </c>
       <c r="B29" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="C29" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="D29" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="E29" t="s">
         <v>195</v>
@@ -1684,16 +1685,16 @@
     </row>
     <row r="30" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B30" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="C30" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="D30" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="E30" t="s">
         <v>195</v>
@@ -1701,16 +1702,16 @@
     </row>
     <row r="31" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>98</v>
+        <v>86</v>
       </c>
       <c r="B31" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="C31" t="s">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="D31" t="s">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="E31" t="s">
         <v>195</v>
@@ -1718,64 +1719,64 @@
     </row>
     <row r="32" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
+        <v>98</v>
+      </c>
+      <c r="B32" t="s">
+        <v>96</v>
+      </c>
+      <c r="C32" t="s">
+        <v>95</v>
+      </c>
+      <c r="D32" t="s">
+        <v>97</v>
+      </c>
+      <c r="E32" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
         <v>99</v>
       </c>
-      <c r="B32" t="s">
+      <c r="B33" t="s">
         <v>100</v>
       </c>
-      <c r="C32" t="s">
+      <c r="C33" t="s">
         <v>101</v>
       </c>
-      <c r="D32" t="s">
+      <c r="D33" t="s">
         <v>102</v>
       </c>
-      <c r="E32" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
+      <c r="E33" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
         <v>103</v>
       </c>
-      <c r="B33" t="s">
+      <c r="B34" t="s">
         <v>106</v>
       </c>
-      <c r="C33" t="s">
+      <c r="C34" t="s">
         <v>104</v>
       </c>
-      <c r="D33" t="s">
+      <c r="D34" t="s">
         <v>105</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>107</v>
-      </c>
-      <c r="B34" t="s">
-        <v>108</v>
-      </c>
-      <c r="C34" t="s">
-        <v>109</v>
-      </c>
-      <c r="D34" t="s">
-        <v>110</v>
-      </c>
-      <c r="E34" t="s">
-        <v>195</v>
       </c>
     </row>
     <row r="35" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="B35" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="C35" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="D35" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="E35" t="s">
         <v>195</v>
@@ -1783,16 +1784,16 @@
     </row>
     <row r="36" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="B36" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="C36" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="D36" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="E36" t="s">
         <v>195</v>
@@ -1800,16 +1801,16 @@
     </row>
     <row r="37" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B37" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="C37" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="D37" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="E37" t="s">
         <v>195</v>
@@ -1817,16 +1818,16 @@
     </row>
     <row r="38" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="B38" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="C38" t="s">
-        <v>129</v>
+        <v>119</v>
       </c>
       <c r="D38" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="E38" t="s">
         <v>195</v>
@@ -1834,16 +1835,16 @@
     </row>
     <row r="39" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="B39" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="C39" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="D39" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="E39" t="s">
         <v>195</v>
@@ -1851,16 +1852,16 @@
     </row>
     <row r="40" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>137</v>
+        <v>123</v>
       </c>
       <c r="B40" t="s">
-        <v>138</v>
+        <v>125</v>
       </c>
       <c r="C40" t="s">
-        <v>135</v>
+        <v>124</v>
       </c>
       <c r="D40" t="s">
-        <v>136</v>
+        <v>126</v>
       </c>
       <c r="E40" t="s">
         <v>195</v>
@@ -1868,78 +1869,78 @@
     </row>
     <row r="41" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
+        <v>137</v>
+      </c>
+      <c r="B41" t="s">
+        <v>138</v>
+      </c>
+      <c r="C41" t="s">
+        <v>135</v>
+      </c>
+      <c r="D41" t="s">
+        <v>136</v>
+      </c>
+      <c r="E41" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
         <v>144</v>
       </c>
-      <c r="B41" t="s">
+      <c r="B42" t="s">
         <v>145</v>
       </c>
-      <c r="C41" t="s">
+      <c r="C42" t="s">
         <v>146</v>
       </c>
-      <c r="D41" t="s">
+      <c r="D42" t="s">
         <v>147</v>
       </c>
-      <c r="E41" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
-        <v>13</v>
-      </c>
-      <c r="B42" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C42" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D42" t="s">
-        <v>12</v>
+      <c r="E42" t="s">
+        <v>195</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
+        <v>13</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D43" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
         <v>224</v>
       </c>
-      <c r="B43" t="s">
+      <c r="B44" t="s">
         <v>149</v>
       </c>
-      <c r="C43" t="s">
+      <c r="C44" t="s">
         <v>148</v>
       </c>
-      <c r="D43" t="s">
+      <c r="D44" t="s">
         <v>114</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
-        <v>153</v>
-      </c>
-      <c r="B44" t="s">
-        <v>150</v>
-      </c>
-      <c r="C44" t="s">
-        <v>151</v>
-      </c>
-      <c r="D44" t="s">
-        <v>152</v>
-      </c>
-      <c r="E44" t="s">
-        <v>195</v>
       </c>
     </row>
     <row r="45" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B45" t="s">
-        <v>157</v>
+        <v>150</v>
       </c>
       <c r="C45" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="D45" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="E45" t="s">
         <v>195</v>
@@ -1947,64 +1948,64 @@
     </row>
     <row r="46" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
+        <v>154</v>
+      </c>
+      <c r="B46" t="s">
+        <v>157</v>
+      </c>
+      <c r="C46" t="s">
+        <v>155</v>
+      </c>
+      <c r="D46" t="s">
+        <v>156</v>
+      </c>
+      <c r="E46" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
         <v>173</v>
       </c>
-      <c r="B46" t="s">
+      <c r="B47" t="s">
         <v>170</v>
       </c>
-      <c r="C46" t="s">
+      <c r="C47" t="s">
         <v>171</v>
       </c>
-      <c r="D46" t="s">
+      <c r="D47" t="s">
         <v>172</v>
       </c>
-      <c r="E46" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A47" s="5" t="s">
+      <c r="E47" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A48" s="5" t="s">
         <v>225</v>
       </c>
-      <c r="B47" t="s">
+      <c r="B48" t="s">
         <v>223</v>
       </c>
-      <c r="C47" t="s">
+      <c r="C48" t="s">
         <v>222</v>
       </c>
-      <c r="D47" t="s">
+      <c r="D48" t="s">
         <v>114</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A48" t="s">
-        <v>131</v>
-      </c>
-      <c r="B48" t="s">
-        <v>132</v>
-      </c>
-      <c r="C48" t="s">
-        <v>133</v>
-      </c>
-      <c r="D48" t="s">
-        <v>134</v>
-      </c>
-      <c r="E48" t="s">
-        <v>195</v>
       </c>
     </row>
     <row r="49" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>203</v>
-      </c>
-      <c r="B49" s="1" t="s">
-        <v>213</v>
-      </c>
-      <c r="C49" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="D49" s="3" t="s">
-        <v>202</v>
+        <v>131</v>
+      </c>
+      <c r="B49" t="s">
+        <v>132</v>
+      </c>
+      <c r="C49" t="s">
+        <v>133</v>
+      </c>
+      <c r="D49" t="s">
+        <v>134</v>
       </c>
       <c r="E49" t="s">
         <v>195</v>
@@ -2012,16 +2013,16 @@
     </row>
     <row r="50" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>139</v>
-      </c>
-      <c r="B50" t="s">
-        <v>141</v>
-      </c>
-      <c r="C50" t="s">
-        <v>140</v>
-      </c>
-      <c r="D50" t="s">
-        <v>142</v>
+        <v>203</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="D50" s="3" t="s">
+        <v>202</v>
       </c>
       <c r="E50" t="s">
         <v>195</v>
@@ -2029,118 +2030,118 @@
     </row>
     <row r="51" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>166</v>
+        <v>139</v>
       </c>
       <c r="B51" t="s">
-        <v>167</v>
+        <v>141</v>
       </c>
       <c r="C51" t="s">
-        <v>168</v>
+        <v>140</v>
       </c>
       <c r="D51" t="s">
-        <v>169</v>
-      </c>
-      <c r="E51" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="E51" t="s">
         <v>195</v>
       </c>
     </row>
     <row r="52" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>92</v>
+        <v>166</v>
       </c>
       <c r="B52" t="s">
-        <v>190</v>
+        <v>167</v>
       </c>
       <c r="C52" t="s">
-        <v>93</v>
+        <v>168</v>
       </c>
       <c r="D52" t="s">
-        <v>94</v>
-      </c>
-      <c r="E52" t="s">
+        <v>169</v>
+      </c>
+      <c r="E52" s="4" t="s">
         <v>195</v>
       </c>
     </row>
     <row r="53" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>182</v>
+        <v>92</v>
       </c>
       <c r="B53" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="C53" t="s">
-        <v>183</v>
+        <v>93</v>
       </c>
       <c r="D53" t="s">
-        <v>184</v>
-      </c>
-      <c r="E53" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="E53" t="s">
         <v>195</v>
       </c>
     </row>
     <row r="54" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>89</v>
+        <v>182</v>
       </c>
       <c r="B54" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="C54" t="s">
-        <v>90</v>
+        <v>183</v>
       </c>
       <c r="D54" t="s">
-        <v>91</v>
-      </c>
-      <c r="E54" t="s">
+        <v>184</v>
+      </c>
+      <c r="E54" s="4" t="s">
         <v>195</v>
       </c>
     </row>
     <row r="55" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>188</v>
+        <v>89</v>
       </c>
       <c r="B55" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="C55" t="s">
-        <v>187</v>
-      </c>
-      <c r="D55" s="3">
-        <v>40</v>
-      </c>
-      <c r="E55" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="D55" t="s">
+        <v>91</v>
+      </c>
+      <c r="E55" t="s">
         <v>195</v>
       </c>
     </row>
     <row r="56" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>160</v>
+        <v>188</v>
       </c>
       <c r="B56" t="s">
-        <v>159</v>
+        <v>186</v>
       </c>
       <c r="C56" t="s">
-        <v>158</v>
-      </c>
-      <c r="D56" t="s">
-        <v>161</v>
-      </c>
-      <c r="E56" t="s">
+        <v>187</v>
+      </c>
+      <c r="D56" s="3">
+        <v>40</v>
+      </c>
+      <c r="E56" s="4" t="s">
         <v>195</v>
       </c>
     </row>
     <row r="57" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="B57" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="C57" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="D57" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="E57" t="s">
         <v>195</v>
@@ -2148,126 +2149,143 @@
     </row>
     <row r="58" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
+        <v>165</v>
+      </c>
+      <c r="B58" t="s">
+        <v>164</v>
+      </c>
+      <c r="C58" t="s">
+        <v>162</v>
+      </c>
+      <c r="D58" t="s">
+        <v>163</v>
+      </c>
+      <c r="E58" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
         <v>174</v>
       </c>
-      <c r="B58" t="s">
+      <c r="B59" t="s">
         <v>176</v>
       </c>
-      <c r="C58" t="s">
+      <c r="C59" t="s">
         <v>175</v>
       </c>
-      <c r="D58" t="s">
+      <c r="D59" t="s">
         <v>177</v>
       </c>
-      <c r="E58" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A59" t="s">
-        <v>229</v>
-      </c>
-      <c r="B59" t="s">
-        <v>226</v>
-      </c>
-      <c r="C59" t="s">
-        <v>227</v>
-      </c>
-      <c r="D59" t="s">
-        <v>228</v>
+      <c r="E59" t="s">
+        <v>195</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
+        <v>229</v>
+      </c>
+      <c r="B60" t="s">
+        <v>226</v>
+      </c>
+      <c r="C60" t="s">
+        <v>227</v>
+      </c>
+      <c r="D60" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
         <v>230</v>
       </c>
-      <c r="B60" t="s">
+      <c r="B61" t="s">
         <v>232</v>
       </c>
-      <c r="C60" t="s">
+      <c r="C61" t="s">
         <v>231</v>
       </c>
-      <c r="D60" t="s">
+      <c r="D61" t="s">
         <v>233</v>
       </c>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="E61" t="s">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E62" t="s">
         <v>196</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A62" t="s">
-        <v>237</v>
-      </c>
-      <c r="B62" t="s">
-        <v>236</v>
-      </c>
-      <c r="C62" t="s">
-        <v>234</v>
-      </c>
-      <c r="D62" t="s">
-        <v>235</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="B63" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="C63" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="D63" t="s">
-        <v>241</v>
+        <v>235</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="B64" t="s">
-        <v>245</v>
+        <v>239</v>
       </c>
       <c r="C64" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="D64" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="B65" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="C65" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="D65" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
+        <v>246</v>
+      </c>
+      <c r="B66" t="s">
+        <v>249</v>
+      </c>
+      <c r="C66" t="s">
+        <v>248</v>
+      </c>
+      <c r="D66" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
         <v>250</v>
       </c>
-      <c r="B66" t="s">
+      <c r="B67" t="s">
         <v>253</v>
       </c>
-      <c r="C66" t="s">
+      <c r="C67" t="s">
         <v>251</v>
       </c>
-      <c r="D66" t="s">
+      <c r="D67" t="s">
         <v>252</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E58" xr:uid="{2CF9E297-72DE-4386-8002-570237626454}">
+  <autoFilter ref="A1:E59" xr:uid="{2CF9E297-72DE-4386-8002-570237626454}">
     <filterColumn colId="4">
       <filters blank="1">
         <filter val="GAP"/>
@@ -2279,14 +2297,14 @@
   </sortState>
   <hyperlinks>
     <hyperlink ref="B3" r:id="rId1" xr:uid="{88D7FD61-7495-433B-BB0E-0F6A89ABE74A}"/>
-    <hyperlink ref="B42" r:id="rId2" xr:uid="{63CC93D1-B3B9-4AD9-8A03-C49E71BB178F}"/>
+    <hyperlink ref="B43" r:id="rId2" xr:uid="{63CC93D1-B3B9-4AD9-8A03-C49E71BB178F}"/>
     <hyperlink ref="B5" r:id="rId3" xr:uid="{BE3001C8-C6F4-4958-8E83-375C8631FFD0}"/>
     <hyperlink ref="C6" r:id="rId4" xr:uid="{B0629CDA-CE4C-4A68-98F2-514ED65E6764}"/>
     <hyperlink ref="B6" r:id="rId5" xr:uid="{E8D94EF1-4592-45B9-B8B2-6EE34CDA156B}"/>
-    <hyperlink ref="C20" r:id="rId6" xr:uid="{5F8F8A1D-DECA-423A-B681-8EB6D1C72089}"/>
-    <hyperlink ref="C23" r:id="rId7" xr:uid="{EA0AE655-D84E-4CA0-B64D-234DB4B1F86A}"/>
-    <hyperlink ref="B17" r:id="rId8" xr:uid="{962EF1F7-F1F1-425B-85D9-C19696DDDA8A}"/>
-    <hyperlink ref="C49" r:id="rId9" xr:uid="{9CC374CE-9746-4369-A4C1-2ED078F270F4}"/>
+    <hyperlink ref="C21" r:id="rId6" xr:uid="{5F8F8A1D-DECA-423A-B681-8EB6D1C72089}"/>
+    <hyperlink ref="C24" r:id="rId7" xr:uid="{EA0AE655-D84E-4CA0-B64D-234DB4B1F86A}"/>
+    <hyperlink ref="B18" r:id="rId8" xr:uid="{962EF1F7-F1F1-425B-85D9-C19696DDDA8A}"/>
+    <hyperlink ref="C50" r:id="rId9" xr:uid="{9CC374CE-9746-4369-A4C1-2ED078F270F4}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId10"/>
